--- a/src/main/resources/baseFiles/excel/LastCheckSheet.xlsx
+++ b/src/main/resources/baseFiles/excel/LastCheckSheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="14540"/>
+    <workbookView windowWidth="24680" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1175,10 +1175,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K384"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="10" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="12.6875" style="1"/>
+    <col min="4" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1"/>
@@ -5217,39 +5219,601 @@
       <c r="I336"/>
       <c r="J336"/>
     </row>
-    <row r="337" spans="11:11">
+    <row r="337" spans="1:11">
+      <c r="A337"/>
+      <c r="B337"/>
+      <c r="C337"/>
+      <c r="D337"/>
+      <c r="E337"/>
+      <c r="F337"/>
+      <c r="G337"/>
+      <c r="H337"/>
+      <c r="I337"/>
+      <c r="J337"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="11:11">
+    <row r="338" spans="1:11">
+      <c r="A338"/>
+      <c r="B338"/>
+      <c r="C338"/>
+      <c r="D338"/>
+      <c r="E338"/>
+      <c r="F338"/>
+      <c r="G338"/>
+      <c r="H338"/>
+      <c r="I338"/>
+      <c r="J338"/>
       <c r="K338" s="1"/>
     </row>
-    <row r="339" spans="11:11">
+    <row r="339" spans="1:11">
+      <c r="A339"/>
+      <c r="B339"/>
+      <c r="C339"/>
+      <c r="D339"/>
+      <c r="E339"/>
+      <c r="F339"/>
+      <c r="G339"/>
+      <c r="H339"/>
+      <c r="I339"/>
+      <c r="J339"/>
       <c r="K339" s="1"/>
     </row>
-    <row r="341" spans="11:11">
+    <row r="340" spans="1:10">
+      <c r="A340"/>
+      <c r="B340"/>
+      <c r="C340"/>
+      <c r="D340"/>
+      <c r="E340"/>
+      <c r="F340"/>
+      <c r="G340"/>
+      <c r="H340"/>
+      <c r="I340"/>
+      <c r="J340"/>
+    </row>
+    <row r="341" spans="1:11">
+      <c r="A341"/>
+      <c r="B341"/>
+      <c r="C341"/>
+      <c r="D341"/>
+      <c r="E341"/>
+      <c r="F341"/>
+      <c r="G341"/>
+      <c r="H341"/>
+      <c r="I341"/>
+      <c r="J341"/>
       <c r="K341" s="1"/>
     </row>
-    <row r="343" spans="11:11">
+    <row r="342" spans="1:10">
+      <c r="A342"/>
+      <c r="B342"/>
+      <c r="C342"/>
+      <c r="D342"/>
+      <c r="E342"/>
+      <c r="F342"/>
+      <c r="G342"/>
+      <c r="H342"/>
+      <c r="I342"/>
+      <c r="J342"/>
+    </row>
+    <row r="343" spans="1:11">
+      <c r="A343"/>
+      <c r="B343"/>
+      <c r="C343"/>
+      <c r="D343"/>
+      <c r="E343"/>
+      <c r="F343"/>
+      <c r="G343"/>
+      <c r="H343"/>
+      <c r="I343"/>
+      <c r="J343"/>
       <c r="K343" s="1"/>
     </row>
-    <row r="348" spans="11:11">
+    <row r="344" spans="1:10">
+      <c r="A344"/>
+      <c r="B344"/>
+      <c r="C344"/>
+      <c r="D344"/>
+      <c r="E344"/>
+      <c r="F344"/>
+      <c r="G344"/>
+      <c r="H344"/>
+      <c r="I344"/>
+      <c r="J344"/>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="A345"/>
+      <c r="B345"/>
+      <c r="C345"/>
+      <c r="D345"/>
+      <c r="E345"/>
+      <c r="F345"/>
+      <c r="G345"/>
+      <c r="H345"/>
+      <c r="I345"/>
+      <c r="J345"/>
+    </row>
+    <row r="346" spans="1:10">
+      <c r="A346"/>
+      <c r="B346"/>
+      <c r="C346"/>
+      <c r="D346"/>
+      <c r="E346"/>
+      <c r="F346"/>
+      <c r="G346"/>
+      <c r="H346"/>
+      <c r="I346"/>
+      <c r="J346"/>
+    </row>
+    <row r="347" spans="1:10">
+      <c r="A347"/>
+      <c r="B347"/>
+      <c r="C347"/>
+      <c r="D347"/>
+      <c r="E347"/>
+      <c r="F347"/>
+      <c r="G347"/>
+      <c r="H347"/>
+      <c r="I347"/>
+      <c r="J347"/>
+    </row>
+    <row r="348" spans="1:11">
+      <c r="A348"/>
+      <c r="B348"/>
+      <c r="C348"/>
+      <c r="D348"/>
+      <c r="E348"/>
+      <c r="F348"/>
+      <c r="G348"/>
+      <c r="H348"/>
+      <c r="I348"/>
+      <c r="J348"/>
       <c r="K348" s="1"/>
     </row>
-    <row r="349" spans="11:11">
+    <row r="349" spans="1:11">
+      <c r="A349"/>
+      <c r="B349"/>
+      <c r="C349"/>
+      <c r="D349"/>
+      <c r="E349"/>
+      <c r="F349"/>
+      <c r="G349"/>
+      <c r="H349"/>
+      <c r="I349"/>
+      <c r="J349"/>
       <c r="K349" s="1"/>
     </row>
-    <row r="350" spans="11:11">
+    <row r="350" spans="1:11">
+      <c r="A350"/>
+      <c r="B350"/>
+      <c r="C350"/>
+      <c r="D350"/>
+      <c r="E350"/>
+      <c r="F350"/>
+      <c r="G350"/>
+      <c r="H350"/>
+      <c r="I350"/>
+      <c r="J350"/>
       <c r="K350" s="1"/>
     </row>
-    <row r="351" spans="11:11">
+    <row r="351" spans="1:11">
+      <c r="A351"/>
+      <c r="B351"/>
+      <c r="C351"/>
+      <c r="D351"/>
+      <c r="E351"/>
+      <c r="F351"/>
+      <c r="G351"/>
+      <c r="H351"/>
+      <c r="I351"/>
+      <c r="J351"/>
       <c r="K351" s="1"/>
     </row>
+    <row r="352" spans="1:10">
+      <c r="A352"/>
+      <c r="B352"/>
+      <c r="C352"/>
+      <c r="D352"/>
+      <c r="E352"/>
+      <c r="F352"/>
+      <c r="G352"/>
+      <c r="H352"/>
+      <c r="I352"/>
+      <c r="J352"/>
+    </row>
+    <row r="353" spans="1:10">
+      <c r="A353"/>
+      <c r="B353"/>
+      <c r="C353"/>
+      <c r="D353"/>
+      <c r="E353"/>
+      <c r="F353"/>
+      <c r="G353"/>
+      <c r="H353"/>
+      <c r="I353"/>
+      <c r="J353"/>
+    </row>
+    <row r="354" spans="1:10">
+      <c r="A354"/>
+      <c r="B354"/>
+      <c r="C354"/>
+      <c r="D354"/>
+      <c r="E354"/>
+      <c r="F354"/>
+      <c r="G354"/>
+      <c r="H354"/>
+      <c r="I354"/>
+      <c r="J354"/>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="A355"/>
+      <c r="B355"/>
+      <c r="C355"/>
+      <c r="D355"/>
+      <c r="E355"/>
+      <c r="F355"/>
+      <c r="G355"/>
+      <c r="H355"/>
+      <c r="I355"/>
+      <c r="J355"/>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="A356"/>
+      <c r="B356"/>
+      <c r="C356"/>
+      <c r="D356"/>
+      <c r="E356"/>
+      <c r="F356"/>
+      <c r="G356"/>
+      <c r="H356"/>
+      <c r="I356"/>
+      <c r="J356"/>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="A357"/>
+      <c r="B357"/>
+      <c r="C357"/>
+      <c r="D357"/>
+      <c r="E357"/>
+      <c r="F357"/>
+      <c r="G357"/>
+      <c r="H357"/>
+      <c r="I357"/>
+      <c r="J357"/>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="A358"/>
+      <c r="B358"/>
+      <c r="C358"/>
+      <c r="D358"/>
+      <c r="E358"/>
+      <c r="F358"/>
+      <c r="G358"/>
+      <c r="H358"/>
+      <c r="I358"/>
+      <c r="J358"/>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="A359"/>
+      <c r="B359"/>
+      <c r="C359"/>
+      <c r="D359"/>
+      <c r="E359"/>
+      <c r="F359"/>
+      <c r="G359"/>
+      <c r="H359"/>
+      <c r="I359"/>
+      <c r="J359"/>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="A360"/>
+      <c r="B360"/>
+      <c r="C360"/>
+      <c r="D360"/>
+      <c r="E360"/>
+      <c r="F360"/>
+      <c r="G360"/>
+      <c r="H360"/>
+      <c r="I360"/>
+      <c r="J360"/>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="A361"/>
+      <c r="B361"/>
+      <c r="C361"/>
+      <c r="D361"/>
+      <c r="E361"/>
+      <c r="F361"/>
+      <c r="G361"/>
+      <c r="H361"/>
+      <c r="I361"/>
+      <c r="J361"/>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="A362"/>
+      <c r="B362"/>
+      <c r="C362"/>
+      <c r="D362"/>
+      <c r="E362"/>
+      <c r="F362"/>
+      <c r="G362"/>
+      <c r="H362"/>
+      <c r="I362"/>
+      <c r="J362"/>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="A363"/>
+      <c r="B363"/>
+      <c r="C363"/>
+      <c r="D363"/>
+      <c r="E363"/>
+      <c r="F363"/>
+      <c r="G363"/>
+      <c r="H363"/>
+      <c r="I363"/>
+      <c r="J363"/>
+    </row>
+    <row r="364" spans="1:10">
+      <c r="A364"/>
+      <c r="B364"/>
+      <c r="C364"/>
+      <c r="D364"/>
+      <c r="E364"/>
+      <c r="F364"/>
+      <c r="G364"/>
+      <c r="H364"/>
+      <c r="I364"/>
+      <c r="J364"/>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="A365"/>
+      <c r="B365"/>
+      <c r="C365"/>
+      <c r="D365"/>
+      <c r="E365"/>
+      <c r="F365"/>
+      <c r="G365"/>
+      <c r="H365"/>
+      <c r="I365"/>
+      <c r="J365"/>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="A366"/>
+      <c r="B366"/>
+      <c r="C366"/>
+      <c r="D366"/>
+      <c r="E366"/>
+      <c r="F366"/>
+      <c r="G366"/>
+      <c r="H366"/>
+      <c r="I366"/>
+      <c r="J366"/>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="A367"/>
+      <c r="B367"/>
+      <c r="C367"/>
+      <c r="D367"/>
+      <c r="E367"/>
+      <c r="F367"/>
+      <c r="G367"/>
+      <c r="H367"/>
+      <c r="I367"/>
+      <c r="J367"/>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="A368"/>
+      <c r="B368"/>
+      <c r="C368"/>
+      <c r="D368"/>
+      <c r="E368"/>
+      <c r="F368"/>
+      <c r="G368"/>
+      <c r="H368"/>
+      <c r="I368"/>
+      <c r="J368"/>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="A369"/>
+      <c r="B369"/>
+      <c r="C369"/>
+      <c r="D369"/>
+      <c r="E369"/>
+      <c r="F369"/>
+      <c r="G369"/>
+      <c r="H369"/>
+      <c r="I369"/>
+      <c r="J369"/>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+      <c r="D370"/>
+      <c r="E370"/>
+      <c r="F370"/>
+      <c r="G370"/>
+      <c r="H370"/>
+      <c r="I370"/>
+      <c r="J370"/>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+      <c r="D371"/>
+      <c r="E371"/>
+      <c r="F371"/>
+      <c r="G371"/>
+      <c r="H371"/>
+      <c r="I371"/>
+      <c r="J371"/>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+      <c r="D372"/>
+      <c r="E372"/>
+      <c r="F372"/>
+      <c r="G372"/>
+      <c r="H372"/>
+      <c r="I372"/>
+      <c r="J372"/>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="A373"/>
+      <c r="B373"/>
+      <c r="C373"/>
+      <c r="D373"/>
+      <c r="E373"/>
+      <c r="F373"/>
+      <c r="G373"/>
+      <c r="H373"/>
+      <c r="I373"/>
+      <c r="J373"/>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374"/>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
+      <c r="I374"/>
+      <c r="J374"/>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="A375"/>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
+      <c r="I375"/>
+      <c r="J375"/>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+      <c r="E376"/>
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
+      <c r="I376"/>
+      <c r="J376"/>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="A377"/>
+      <c r="B377"/>
+      <c r="C377"/>
+      <c r="D377"/>
+      <c r="E377"/>
+      <c r="F377"/>
+      <c r="G377"/>
+      <c r="H377"/>
+      <c r="I377"/>
+      <c r="J377"/>
+    </row>
+    <row r="378" spans="1:10">
+      <c r="A378"/>
+      <c r="B378"/>
+      <c r="C378"/>
+      <c r="D378"/>
+      <c r="E378"/>
+      <c r="F378"/>
+      <c r="G378"/>
+      <c r="H378"/>
+      <c r="I378"/>
+      <c r="J378"/>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="A379"/>
+      <c r="B379"/>
+      <c r="C379"/>
+      <c r="D379"/>
+      <c r="E379"/>
+      <c r="F379"/>
+      <c r="G379"/>
+      <c r="H379"/>
+      <c r="I379"/>
+      <c r="J379"/>
+    </row>
+    <row r="380" spans="1:10">
+      <c r="A380"/>
+      <c r="B380"/>
+      <c r="C380"/>
+      <c r="D380"/>
+      <c r="E380"/>
+      <c r="F380"/>
+      <c r="G380"/>
+      <c r="H380"/>
+      <c r="I380"/>
+      <c r="J380"/>
+    </row>
+    <row r="381" spans="1:10">
+      <c r="A381"/>
+      <c r="B381"/>
+      <c r="C381"/>
+      <c r="D381"/>
+      <c r="E381"/>
+      <c r="F381"/>
+      <c r="G381"/>
+      <c r="H381"/>
+      <c r="I381"/>
+      <c r="J381"/>
+    </row>
+    <row r="382" spans="1:10">
+      <c r="A382"/>
+      <c r="B382"/>
+      <c r="C382"/>
+      <c r="D382"/>
+      <c r="E382"/>
+      <c r="F382"/>
+      <c r="G382"/>
+      <c r="H382"/>
+      <c r="I382"/>
+      <c r="J382"/>
+    </row>
+    <row r="383" spans="1:10">
+      <c r="A383"/>
+      <c r="B383"/>
+      <c r="C383"/>
+      <c r="D383"/>
+      <c r="E383"/>
+      <c r="F383"/>
+      <c r="G383"/>
+      <c r="H383"/>
+      <c r="I383"/>
+      <c r="J383"/>
+    </row>
+    <row r="384" spans="1:10">
+      <c r="A384"/>
+      <c r="B384"/>
+      <c r="C384"/>
+      <c r="D384"/>
+      <c r="E384"/>
+      <c r="F384"/>
+      <c r="G384"/>
+      <c r="H384"/>
+      <c r="I384"/>
+      <c r="J384"/>
+    </row>
   </sheetData>
-  <sortState ref="A1:J370">
-    <sortCondition ref="A148"/>
+  <sortState ref="A1:J446">
+    <sortCondition ref="I1:I446"/>
+    <sortCondition ref="J1:J446"/>
+    <sortCondition ref="D1:D446"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B370" r:id="rId1"/>
+    <hyperlink ref="F424" r:id="rId1"/>
+    <hyperlink ref="B445" r:id="rId2"/>
+    <hyperlink ref="F408" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
